--- a/data/b2_indio/B2 Índio 12-2025.xlsx
+++ b/data/b2_indio/B2 Índio 12-2025.xlsx
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>51376.75</v>
+        <v>51042.49</v>
       </c>
     </row>
     <row r="3">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>3634.62</v>
+        <v>3500.19</v>
       </c>
     </row>
     <row r="4">
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1704.7</v>
+        <v>2359.86</v>
       </c>
     </row>
     <row r="6">
@@ -5013,16 +5013,16 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>1845.75</v>
+        <v>2034.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46004</v>
+        <v>46005</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1324.5</v>
+        <v>1083.96</v>
       </c>
     </row>
     <row r="8">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3669.43</v>
+        <v>3650.45</v>
       </c>
     </row>
     <row r="9">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>10296.36</v>
+        <v>9630.620000000001</v>
       </c>
     </row>
     <row r="10">
@@ -5089,25 +5089,25 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1554.69</v>
+        <v>1510.48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46011</v>
+        <v>46007</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>18125.84</v>
+        <v>1587.94</v>
       </c>
     </row>
     <row r="12">
@@ -5116,70 +5116,70 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1540.88</v>
+        <v>18214.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46011</v>
+        <v>46012</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1099.7</v>
+        <v>3470.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46012</v>
+        <v>46015</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1513.67</v>
+        <v>1122.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46012</v>
+        <v>46016</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3605.45</v>
+        <v>1054.34</v>
       </c>
     </row>
     <row r="16">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3300.05</v>
+        <v>3609.02</v>
       </c>
     </row>
     <row r="17">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>1493.3</v>
+        <v>1427.14</v>
       </c>
     </row>
   </sheetData>
